--- a/_resultados-MovieLens.xlsx
+++ b/_resultados-MovieLens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95211B9-FAF7-4CBB-9A4E-7385BA8F5E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A51B4F1-6EA9-43B8-8A24-8F4813A524CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="734" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="734" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="capa" sheetId="19" r:id="rId1"/>
